--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/SOUTH_CAROLINA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/SOUTH_CAROLINA_2020.xlsx
@@ -1345,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="56">
@@ -1381,7 +1381,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="58">
@@ -2263,7 +2263,7 @@
         <v>7</v>
       </c>
       <c r="D106">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="107">
@@ -2569,7 +2569,7 @@
         <v>7</v>
       </c>
       <c r="D123">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="124">
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="D124">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="125">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C131">
@@ -3199,7 +3199,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="159">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C189">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C212">
@@ -4344,14 +4344,14 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C222">
         <v>7</v>
       </c>
       <c r="D222">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="223">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C231">
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="D239">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="240">
@@ -5233,7 +5233,7 @@
         <v>7</v>
       </c>
       <c r="D271">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="272">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C308">
@@ -6133,7 +6133,7 @@
         <v>7</v>
       </c>
       <c r="D321">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="322">
@@ -6601,7 +6601,7 @@
         <v>7</v>
       </c>
       <c r="D347">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="348">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C359">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C364">
@@ -7627,7 +7627,7 @@
         <v>7</v>
       </c>
       <c r="D404">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="405">
@@ -8275,7 +8275,7 @@
         <v>7</v>
       </c>
       <c r="D440">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="441">
@@ -8977,7 +8977,7 @@
         <v>7</v>
       </c>
       <c r="D479">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="480">
@@ -10273,7 +10273,7 @@
         <v>7</v>
       </c>
       <c r="D551">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="552">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C563">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C599">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C600">
@@ -11299,7 +11299,7 @@
         <v>7</v>
       </c>
       <c r="D608">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="609">
@@ -11371,7 +11371,7 @@
         <v>7</v>
       </c>
       <c r="D612">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="613">
@@ -11479,7 +11479,7 @@
         <v>7</v>
       </c>
       <c r="D618">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="619">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C628">
@@ -12523,7 +12523,7 @@
         <v>7</v>
       </c>
       <c r="D676">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="677">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C711">
@@ -13423,7 +13423,7 @@
         <v>7</v>
       </c>
       <c r="D726">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="727">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C779">
@@ -14557,7 +14557,7 @@
         <v>7</v>
       </c>
       <c r="D789">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="790">
@@ -14809,7 +14809,7 @@
         <v>7</v>
       </c>
       <c r="D803">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="804">
@@ -15007,7 +15007,7 @@
         <v>7</v>
       </c>
       <c r="D814">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="815">
@@ -15259,7 +15259,7 @@
         <v>7</v>
       </c>
       <c r="D828">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="829">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Amaxac De Guerero</t>
+          <t>Amaxac De Guerrero</t>
         </is>
       </c>
       <c r="C887">
@@ -16573,7 +16573,7 @@
         <v>7</v>
       </c>
       <c r="D901">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="902">
@@ -17131,7 +17131,7 @@
         <v>7</v>
       </c>
       <c r="D932">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="933">
@@ -17743,7 +17743,7 @@
         <v>7</v>
       </c>
       <c r="D966">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="967">
@@ -18067,7 +18067,7 @@
         <v>7</v>
       </c>
       <c r="D984">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="985">
@@ -18373,7 +18373,7 @@
         <v>7</v>
       </c>
       <c r="D1001">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="1002">
@@ -18661,7 +18661,7 @@
         <v>7</v>
       </c>
       <c r="D1017">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="1018">
@@ -18805,7 +18805,7 @@
         <v>7</v>
       </c>
       <c r="D1025">
-        <v>0.0009714127116291979</v>
+        <v>0.000971412711629198</v>
       </c>
     </row>
     <row r="1026">
